--- a/AAII_Financials/Quarterly/DAL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DAL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="92">
   <si>
     <t>DAL</t>
   </si>
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>19757000</v>
+      </c>
+      <c r="E8" s="3">
         <v>15854000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>16003000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>16673000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>16648000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>14040000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>15559000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>15677000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>16658000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>13748000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>14223000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>15488000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>15578000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>12759000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>13435000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>13975000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>13824000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>9348000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>9470000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>9154000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>7126000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4150000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>3973000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3062000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1468000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>8592000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>11439000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>12560000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>12536000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>10472000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>10742000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>11953000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>11775000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>9968000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>10228000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>11061000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>10747000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>9101000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>9458000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>10483000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>16122000</v>
+      </c>
+      <c r="E9" s="3">
         <v>13459000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>12814000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>13182000</v>
       </c>
-      <c r="G9" s="3">
-        <v>12727000</v>
-      </c>
       <c r="H9" s="3">
+        <v>12673000</v>
+      </c>
+      <c r="I9" s="3">
         <v>11657000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>12042000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>12348000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>12526000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>11455000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>10348000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>11793000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>11392000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>10606000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>7189000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>7662000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>7824000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>6084000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>5267000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>5006000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4425000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3652000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3019000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>2585000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2123000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>4900000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>5104000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>5473000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>5493000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>5068000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>5284000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>5600000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>5581000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>4914000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>4385000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>4878000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>4533000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>4170000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>3993000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>4281000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3635000</v>
+      </c>
+      <c r="E10" s="3">
         <v>2395000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3189000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3491000</v>
       </c>
-      <c r="G10" s="3">
-        <v>3921000</v>
-      </c>
       <c r="H10" s="3">
+        <v>3975000</v>
+      </c>
+      <c r="I10" s="3">
         <v>2383000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3517000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3329000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4132000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2293000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>3875000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>3695000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4186000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>2153000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>6246000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>6313000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>6000000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3264000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>4203000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>4148000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2701000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>498000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>954000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>477000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>-655000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3692000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>6335000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>7087000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>7043000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>5404000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>5458000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>6353000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>6194000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>5054000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>5843000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>6183000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>6214000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>4931000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>5465000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>6202000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,19 +1248,20 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3">
         <v>314000</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
@@ -1255,11 +1269,11 @@
       <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="3">
         <v>324000</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -1267,11 +1281,11 @@
       <c r="L12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="3">
         <v>340000</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>8</v>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,85 +1496,88 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-649000</v>
+      </c>
+      <c r="E14" s="3">
         <v>554000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-201000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-294000</v>
       </c>
-      <c r="G14" s="3">
-        <v>-769000</v>
-      </c>
       <c r="H14" s="3">
+        <v>-754000</v>
+      </c>
+      <c r="I14" s="3">
         <v>40000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>266000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-374000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>229000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>258000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-347000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>198000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-96000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>764000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-124000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>34000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>41000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>20000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>37000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-1606000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-1470000</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-1174000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-930000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>4030000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>1174000</v>
-      </c>
-      <c r="AB14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>8</v>
@@ -1574,8 +1594,8 @@
       <c r="AG14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
+      <c r="AH14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AI14" s="3">
         <v>0</v>
@@ -1592,139 +1612,145 @@
       <c r="AM14" s="3">
         <v>0</v>
       </c>
-      <c r="AN14" s="3" t="s">
+      <c r="AN14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AO14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AP14" s="3" t="s">
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>656000</v>
+      </c>
+      <c r="E15" s="3">
         <v>635000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>620000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>614000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>602000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>607000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>635000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>643000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>620000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>615000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>610000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>594000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>573000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>564000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>553000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>538000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>510000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>506000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>504000</v>
-      </c>
-      <c r="V15" s="3">
-        <v>501000</v>
       </c>
       <c r="W15" s="3">
         <v>501000</v>
       </c>
       <c r="X15" s="3">
+        <v>501000</v>
+      </c>
+      <c r="Y15" s="3">
         <v>492000</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>499000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>545000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>591000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>678000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>621000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>631000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>713000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>615000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>570000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>573000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>583000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>603000</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>583000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>571000</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>531000</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>537000</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>472000</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>474000</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>18192000</v>
+      </c>
+      <c r="E17" s="3">
         <v>15350000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>14574000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>15019000</v>
       </c>
-      <c r="G17" s="3">
-        <v>14640000</v>
-      </c>
       <c r="H17" s="3">
+        <v>14625000</v>
+      </c>
+      <c r="I17" s="3">
         <v>13511000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>13885000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>14352000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>14438000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>13155000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>12092000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>13586000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>13145000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>12233000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>11965000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>12553000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>12346000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>10156000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>9260000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>7132000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>6336000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5604000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4831000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>9448000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>6283000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>9002000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>10040000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>10489000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>10408000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>9452000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>9651000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>10308000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>10091000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>9124000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>9067000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>9238000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>8765000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>8102000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>8438000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>8514000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1565000</v>
+      </c>
+      <c r="E18" s="3">
         <v>504000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1429000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1654000</v>
       </c>
-      <c r="G18" s="3">
-        <v>2008000</v>
-      </c>
       <c r="H18" s="3">
+        <v>2023000</v>
+      </c>
+      <c r="I18" s="3">
         <v>529000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1674000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1325000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2220000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>593000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2131000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1902000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2433000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>526000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1470000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1422000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1478000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-808000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>210000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2022000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>790000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-1454000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-858000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-6386000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-4815000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-410000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1399000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2071000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2128000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>1020000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1091000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1645000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1684000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>844000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1161000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>1823000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>1982000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>999000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>1020000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>1969000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,210 +2085,214 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>61000</v>
+      </c>
+      <c r="E20" s="3">
         <v>13000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-41000</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="G20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>31000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-10000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>26000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-35000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>30000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>8000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-4000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-13000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>9000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>41000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-350000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-460000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-445000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-392000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-605000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-490000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-14000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-61000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-250000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-473000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-2199000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-197000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-124000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-221000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-74000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>254000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>43000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-298000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-112000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-118000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-47000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-151000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-150000</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-68000</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-69000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2160000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1126000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2090000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2268000</v>
       </c>
-      <c r="G21" s="3">
-        <v>2579000</v>
-      </c>
       <c r="H21" s="3">
+        <v>2594000</v>
+      </c>
+      <c r="I21" s="3">
         <v>1146000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2283000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2003000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2810000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1200000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2745000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2509000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2997000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1049000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2689000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>990000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1037000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-694000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1102000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1532000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>785000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-1023000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-1154000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-6905000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-7101000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>71000</v>
-      </c>
-      <c r="AC21" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD21" s="3" t="s">
         <v>8</v>
@@ -2266,83 +2303,86 @@
       <c r="AF21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AG21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH21" s="3">
         <v>3101000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1678000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1366000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1335000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>2694000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1816000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1825000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1386000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>2380000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>1904000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>144000</v>
+      </c>
+      <c r="E22" s="3">
         <v>151000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>158000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>171000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>172000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>179000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>180000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>173000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>188000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>205000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>207000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>196000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>203000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>227000</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
         <v>0</v>
       </c>
@@ -2400,8 +2440,8 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
-      <c r="AK22" s="3" t="s">
-        <v>8</v>
+      <c r="AK22" s="3">
+        <v>0</v>
       </c>
       <c r="AL22" s="3" t="s">
         <v>8</v>
@@ -2418,252 +2458,261 @@
       <c r="AP22" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ22" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2009000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-214000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1513000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1777000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>2574000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>320000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1202000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1561000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1773000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>122000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2275000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1521000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2317000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-506000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1120000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>962000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1033000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-1200000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-395000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1532000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>776000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1515000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-1108000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-6859000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-7014000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-607000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1398000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1947000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1907000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>946000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1345000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1688000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1386000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>732000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>1043000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>1776000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>1831000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>849000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>952000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>1900000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>405000</v>
+      </c>
+      <c r="E24" s="3">
         <v>75000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>294000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>360000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>444000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>80000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>359000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>289000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>468000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>85000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>238000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>413000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>490000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-143000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>291000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>267000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>298000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-260000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>13000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>320000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>124000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-338000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-353000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-1480000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-1297000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-73000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>300000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>452000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>464000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>216000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>326000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>366000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>350000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>175000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>351000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>617000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>645000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>288000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>330000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>641000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1604000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-289000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1219000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1417000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>2130000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>240000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>843000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1272000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1305000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>37000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2037000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1108000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1827000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-363000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>829000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>695000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>735000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-940000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-408000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1212000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>652000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1177000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-755000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-5379000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-5717000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-534000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1098000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>1495000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>1443000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>730000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1019000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>1322000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>1036000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>557000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>692000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>1159000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>1186000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>561000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>622000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>1259000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1604000</v>
+      </c>
+      <c r="E27" s="3">
         <v>-289000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1219000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1417000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2130000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>240000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>843000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1272000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1305000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>37000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2037000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1108000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1827000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-363000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>829000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>695000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>735000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-940000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-408000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1212000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>652000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1177000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-755000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-5379000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-5717000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-534000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>1098000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>1495000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>1443000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>730000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1019000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>1322000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>1036000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>557000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>692000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>1159000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>1186000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>561000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>622000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>1259000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3236,8 +3297,8 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
@@ -3254,11 +3315,11 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-394000</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,252 +3583,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-61000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-13000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>41000</v>
       </c>
-      <c r="F32" s="3" t="s">
+      <c r="G32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-31000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>10000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-26000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>35000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-30000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-8000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>4000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>13000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-9000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-41000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>350000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>460000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>445000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>392000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>605000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>490000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>14000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>61000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>250000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>473000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>2199000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>197000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>1000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>124000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>221000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>74000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-254000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-43000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>298000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>112000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>118000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>47000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>151000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>150000</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>68000</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>69000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1604000</v>
+      </c>
+      <c r="E33" s="3">
         <v>-289000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1219000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1417000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2130000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>240000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>843000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1272000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1305000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>37000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2037000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1108000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1827000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-363000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>829000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>695000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>735000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-940000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-408000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1212000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>652000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1177000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-755000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-5379000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-5717000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-534000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>1098000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>1495000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>1443000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>730000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1019000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1322000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>1036000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>557000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>298000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>1159000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>1186000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>561000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>622000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>1259000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1604000</v>
+      </c>
+      <c r="E35" s="3">
         <v>-289000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1219000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1417000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2130000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>240000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>843000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1272000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1305000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>37000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2037000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1108000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1827000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-363000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>829000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>695000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>735000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-940000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-408000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1212000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>652000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1177000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-755000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-5379000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-5717000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-534000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>1098000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>1495000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>1443000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>730000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1019000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1322000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>1036000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>557000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>298000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>1159000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>1186000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>561000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>622000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>1259000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,130 +4305,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4665000</v>
+      </c>
+      <c r="E41" s="3">
         <v>5053000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4310000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3791000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3331000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3711000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3069000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3969000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4110000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3877000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2741000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2835000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2668000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3215000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3266000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7023000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>9221000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>7705000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>7933000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>8785000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>10357000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>8460000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>8307000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>16477000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>11366000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>5967000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2882000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1899000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2009000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1910000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1565000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1380000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1886000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1447000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1814000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1478000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>2241000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1907000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>2762000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>1638000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4365,61 +4455,61 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>8000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>124000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>589000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>1127000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>2170000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>3368000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>3396000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>3268000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>1345000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>1549000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>2250000</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>3386000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>4417000</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>4873000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>5575000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>5789000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>5048000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>4302000</v>
-      </c>
-      <c r="AB42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC42" s="3" t="s">
         <v>8</v>
@@ -4433,282 +4523,291 @@
       <c r="AF42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AG42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH42" s="3">
         <v>203000</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>478000</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>520000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>523000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>825000</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>960000</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>747000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>743000</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>487000</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>1514000</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4307000</v>
+      </c>
+      <c r="E43" s="3">
         <v>4090000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2850000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3612000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3755000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3652000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3224000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3550000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3812000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3748000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3130000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3214000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3122000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3224000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3176000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3097000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3093000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3039000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2404000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2183000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2258000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1837000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1396000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1503000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1375000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2280000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2854000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>2836000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>2844000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3154000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2314000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>2517000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>2427000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>2568000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>2377000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>2399000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>2164000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>2307000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>2064000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>1996000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2558000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1767000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1601000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1543000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1525000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1486000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1428000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1467000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1486000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1452000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1314000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1507000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1438000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1379000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1424000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1473000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1734000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1292000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1098000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1012000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1005000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>828000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>732000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>746000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>847000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>974000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1251000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1072000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1083000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1071000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1055000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1170000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1589000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1146000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1329000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1136000</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>938000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>855000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>891000</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>775000</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4742,297 +4841,303 @@
       <c r="M45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N45" s="3">
+      <c r="N45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O45" s="3">
         <v>12000</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R45" s="3">
         <v>1877000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1861000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1716000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1434000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1119000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1074000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1173000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1153000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1180000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1256000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1025000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1054000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1262000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1137000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1198000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1061000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1203000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1181000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1219000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>2040000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>1459000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>1110000</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>1087000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>1068000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>1247000</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>1406000</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>14236000</v>
+      </c>
+      <c r="E46" s="3">
         <v>13663000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>10968000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>11230000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>10982000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>11236000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9844000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>11062000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>11588000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>11579000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>10269000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>12255000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>13080000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>13401000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>13011000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>14799000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>17313000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>15720000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>15940000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>17471000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>19666000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>17853000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>17404000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>25030000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>18915000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>10275000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>8249000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>6944000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>7134000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>7196000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>6340000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>6726000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>7641000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>7724000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>7804000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>7083000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>7177000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>6880000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>7451000</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>7329000</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>4041000</v>
+      </c>
+      <c r="E47" s="3">
         <v>3696000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>4222000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>3883000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>3556000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2819000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2846000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>3272000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3022000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3247000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3457000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2291000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2389000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>2249000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>2128000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1585000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1771000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1999000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1712000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1919000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>2143000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>1929000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>1665000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>1562000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>1633000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>3684000</v>
-      </c>
-      <c r="AC47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD47" s="3" t="s">
         <v>8</v>
@@ -5049,8 +5154,8 @@
       <c r="AH47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI47" s="3">
-        <v>0</v>
+      <c r="AI47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ47" s="3">
         <v>0</v>
@@ -5073,252 +5178,261 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>47706000</v>
+      </c>
+      <c r="E48" s="3">
         <v>46882000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>45023000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>45570000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>45261000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>44713000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>43164000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>43548000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>43147000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>42700000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>41428000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>41555000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>40926000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>40316000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>40145000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>38473000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>37708000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>37444000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>35986000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>33643000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>33161000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>32439000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>32262000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>32483000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>34123000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>37132000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>36937000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>36611000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>36071000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>35175000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>34329000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>28565000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>28124000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>27096000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>26563000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>25900000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>25367000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>24817000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>24375000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>24105000</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>15715000</v>
+      </c>
+      <c r="E49" s="3">
         <v>15717000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>15719000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>15721000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>15723000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>15725000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>15728000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>15730000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>15732000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>15734000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>15736000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>15738000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>15741000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>15743000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>15745000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>15747000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>15750000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>15752000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>15754000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>15757000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>15759000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>15762000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>15764000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>15767000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>15770000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>15772000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>14944000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>14602000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>14605000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>14608000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>14611000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>14629000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>14633000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>14637000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>14641000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>14645000</v>
-      </c>
-      <c r="AM49" s="3">
-        <v>14649000</v>
       </c>
       <c r="AN49" s="3">
         <v>14649000</v>
       </c>
       <c r="AO49" s="3">
+        <v>14649000</v>
+      </c>
+      <c r="AP49" s="3">
         <v>14638000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>14642000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4623000</v>
+      </c>
+      <c r="E52" s="3">
         <v>4473000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>5384000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3219000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>2873000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>2849000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3695000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1756000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1708000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1709000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2511000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1408000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1361000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>993000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1259000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1992000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2263000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2833000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3067000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3993000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4580000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>5100000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>4901000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>4234000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1820000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1875000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>4402000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>5062000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>4708000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>4862000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>4986000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>5083000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>5398000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>4621000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>4664000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>4300000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>4622000</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>5113000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>4797000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>4872000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>86321000</v>
+      </c>
+      <c r="E54" s="3">
         <v>84431000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>81317000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>79623000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>78395000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>77342000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>75372000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>75368000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>75197000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>74969000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>73644000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>73247000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>73497000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>73134000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>72288000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>72596000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>74805000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>73748000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>72459000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>72783000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>75309000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>73083000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>71996000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>79076000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>72261000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>68738000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>64532000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>63219000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>62518000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>61841000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>60266000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>55003000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>55796000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>54078000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>53671000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>51928000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>51815000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>51459000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>51261000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>50948000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,740 +6145,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6738000</v>
+      </c>
+      <c r="E57" s="3">
         <v>5969000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5226000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5022000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5063000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4809000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4650000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4545000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4876000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4541000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4446000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5320000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5114000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4754000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>5106000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>4958000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>5353000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>4810000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4240000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4017000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>3930000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3432000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2840000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2403000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2332000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3337000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3266000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>3470000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3359000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>3214000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2976000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>3265000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>3749000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>3351000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>3634000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>3059000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>2726000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>2353000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>2572000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>2567000</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5411000</v>
+      </c>
+      <c r="E58" s="3">
         <v>5025000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3514000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3949000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4065000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4790000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4038000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5196000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4825000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4651000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4842000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3809000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3864000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3960000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2359000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2031000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1936000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1116000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1782000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2296000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>2372000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>2983000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1732000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>5045000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>5230000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>4337000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2287000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2196000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2281000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>3055000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1518000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1176000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1342000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>2289000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>2242000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1224000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>1098000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>1040000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>1131000</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>1092000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>15263000</v>
+      </c>
+      <c r="E59" s="3">
         <v>15752000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>12033000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>12819000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>13391000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>14448000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>11408000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>12424000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>13475000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>14233000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>10952000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>12655000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>14255000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>14878000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>18475000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>18881000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>19035000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>18134000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>14944000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>14611000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>17271000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>14273000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>11355000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>12277000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>12588000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>11718000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>14651000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>14545000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>15524000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>15054000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>14084000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>13717000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>14178000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>14372000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>13083000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>12213000</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>12807000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>12560000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>11536000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>11488000</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>33604000</v>
+      </c>
+      <c r="E60" s="3">
         <v>32699000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>27624000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>28249000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>28554000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>29699000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>26670000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>28118000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>28759000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>28478000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>26418000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>27556000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>28482000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>28417000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>25940000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>25870000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>26324000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>24060000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>20966000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>20924000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>23573000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>20688000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>15927000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>19725000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>20150000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>19392000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>20204000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>20211000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>21164000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>21323000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>18578000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>18158000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>19269000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>20012000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>18959000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>16496000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>16631000</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>15953000</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>15239000</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>15147000</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>15673000</v>
+      </c>
+      <c r="E61" s="3">
         <v>16374000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>17860000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>18129000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>18315000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>18590000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>19833000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>20292000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>21086000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>22758000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>23539000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>24090000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>24786000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>26700000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>20671000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>21202000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>22903000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>24441000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>25138000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>25523000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>26679000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>26061000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>27425000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>29825000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>19412000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>12662000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>8873000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>7923000</v>
-      </c>
-      <c r="AE61" s="3">
-        <v>7710000</v>
       </c>
       <c r="AF61" s="3">
         <v>7710000</v>
       </c>
       <c r="AG61" s="3">
+        <v>7710000</v>
+      </c>
+      <c r="AH61" s="3">
         <v>8253000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>8115000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>8562000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>6360000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>6592000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>7584000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>7916000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>8187000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>6201000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>6473000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3920000</v>
+      </c>
+      <c r="E62" s="3">
         <v>3923000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3994000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3943000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3800000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3707000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3744000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3603000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3507000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3541000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3561000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4301000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4017000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3614000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>19095000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>20934000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>21767000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>22256000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>22468000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>23730000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>23776000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>25852000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>27110000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>26169000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>24009000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>22375000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>20097000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>20017000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>19686000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>19897000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>19748000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>15026000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>15109000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>15149000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>15590000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>13847000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>13789000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>14374000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>17534000</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>16818000</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>64506000</v>
+      </c>
+      <c r="E66" s="3">
         <v>64055000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>60464000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>60801000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>60955000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>61895000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>60079000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>61722000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>62811000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>63818000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>62539000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>64021000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>65397000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>66874000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>65706000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>68006000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>70994000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>70757000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>68572000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>70177000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>74028000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>72601000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>70462000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>75719000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>63571000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>54429000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>49174000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>48151000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>48560000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>48930000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>46579000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>41299000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>42940000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>41521000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>41141000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>37927000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>38336000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>38514000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>38974000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>38438000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>14269000</v>
+      </c>
+      <c r="E72" s="3">
         <v>12931000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>13343000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>12126000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>10833000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>8925000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>8783000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7940000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>6765000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>5622000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>5650000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3613000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2569000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>807000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1170000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>342000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-353000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-1088000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-148000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>259000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-953000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-1605000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-428000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>327000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>5706000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>11423000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>12454000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>11772000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>10686000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>9656000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>10039000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>9696000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>8851000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>8465000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>8256000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>9502000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>8905000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>8226000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>7903000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>11109000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>21815000</v>
+      </c>
+      <c r="E76" s="3">
         <v>20376000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>20853000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>18822000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>17440000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>15447000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>15293000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>13646000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>12386000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>11151000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>11105000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>9226000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8100000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6260000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>6582000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4590000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3811000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2991000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3887000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2606000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>1281000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>482000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1534000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3357000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>8690000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>14309000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>15358000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>15068000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>13958000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>12911000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>13687000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>13704000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>12856000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>12557000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>12530000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>14001000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>13479000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>12945000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>12287000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>12510000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1604000</v>
+      </c>
+      <c r="E81" s="3">
         <v>-289000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1219000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1417000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2130000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>240000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>843000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1272000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1305000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>37000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2037000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1108000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1827000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-363000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>829000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>695000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>735000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-940000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-408000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1212000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>652000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1177000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-755000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-5379000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-5717000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-534000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>1098000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>1495000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>1443000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>730000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1019000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1322000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>1036000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>557000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>298000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>1159000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>1186000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>561000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>622000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>1259000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,53 +8990,54 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>602000</v>
+      </c>
+      <c r="E83" s="3">
         <v>607000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>302000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>643000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>620000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>615000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>270000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>594000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>573000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>564000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>246000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>538000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>510000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>506000</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
       <c r="R83" s="3">
         <v>0</v>
       </c>
@@ -8914,8 +9113,11 @@
       <c r="AP83" s="3">
         <v>0</v>
       </c>
+      <c r="AQ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1595000</v>
+      </c>
+      <c r="E89" s="3">
         <v>2432000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2260000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1847000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1857000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2378000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1894000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1274000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2449000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2408000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>545000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1076000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>2608000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2235000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1188000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>869000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2535000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1771000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>556000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>151000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1866000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>691000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-1286000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-2575000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-290000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>358000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>957000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>2245000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>3272000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1951000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1245000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1499000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>2898000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>1372000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1918000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1645000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>2386000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-801000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>1125000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>1854000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1458000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1200000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-907000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1159000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1209000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1224000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1310000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1328000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1309000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1193000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1602000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1269000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1452000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1000000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2200000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1442000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-958000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1766000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1218000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-830000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-395000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-132000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-302000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-35000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-251000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-308000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-502000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-396000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-393000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-301000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-492000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-392000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-306000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-274000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-361000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-328000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-291000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-1604000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-794000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-680000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1512000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1263000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-728000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1035000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1199000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1224000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1169000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1124000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-809000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-637000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-535000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-131000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1382000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1100000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4735000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1288000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-152000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-749000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-480000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-384000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>26000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-60000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1048000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1144000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-4075000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2971000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-780000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1124000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1563000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1096000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1020000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-903000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1543000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-927000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-1305000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-1295000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-958000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-1708000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>445000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-887000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,34 +10455,35 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>123000</v>
+      </c>
+      <c r="E96" s="3">
         <v>129000</v>
-      </c>
-      <c r="E96" s="3">
-        <v>122000</v>
       </c>
       <c r="F96" s="3">
         <v>122000</v>
       </c>
       <c r="G96" s="3">
+        <v>122000</v>
+      </c>
+      <c r="H96" s="3">
         <v>97000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>99000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>96000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>97000</v>
-      </c>
-      <c r="K96" s="3">
-        <v>64000</v>
       </c>
       <c r="L96" s="3">
         <v>64000</v>
@@ -10260,14 +10494,14 @@
       <c r="N96" s="3">
         <v>64000</v>
       </c>
-      <c r="O96" s="3" t="s">
-        <v>8</v>
+      <c r="O96" s="3">
+        <v>64000</v>
       </c>
       <c r="P96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -10300,52 +10534,55 @@
         <v>0</v>
       </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-260000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-259000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-260000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-228000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-233000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-239000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-240000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-213000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-217000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-215000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-219000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-148000</v>
-      </c>
-      <c r="AN96" s="3">
-        <v>-149000</v>
       </c>
       <c r="AO96" s="3">
         <v>-149000</v>
       </c>
       <c r="AP96" s="3">
+        <v>-149000</v>
+      </c>
+      <c r="AQ96" s="3">
         <v>-150000</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,130 +10953,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-545000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-435000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1002000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-370000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1070000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-634000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1590000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-371000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1512000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-787000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>416000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-800000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1831000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1179000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-305000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1808000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-966000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-1456000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1167000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1565000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-330000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-790000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-5957000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>10247000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>9722000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>5344000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>842000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-1451000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1662000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-609000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-252000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-1203000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>516000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-787000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-250000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-1086000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-1074000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>1680000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-446000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-991000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10876,8 +11125,8 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10954,126 +11203,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-462000</v>
+      </c>
+      <c r="E102" s="3">
         <v>734000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>530000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>442000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-412000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>520000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-865000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-221000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>128000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>984000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>426000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>145000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-605000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-44000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3852000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-2227000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1417000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-434000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1091000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1798000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1562000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-159000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-8291000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>6528000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>5357000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>2731000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1032000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-331000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>44000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>237000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>100000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-612000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>1778000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-371000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>336000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-763000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>334000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-855000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>1124000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-24000</v>
       </c>
     </row>
